--- a/Measurements/C6462020106 Ring harness/batch02/C6462020106 inspection report.xlsx
+++ b/Measurements/C6462020106 Ring harness/batch02/C6462020106 inspection report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manoe\Meng\ManoEng\Measurements\C6462020106 Ring harness\batch02\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EA8FAA3-F961-4D37-A777-2A25E0F8D78B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A14BC4D-1393-4D3A-BD0A-F0750FA0909C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{32BFC42B-CD3D-49FE-8254-52B3F518DB85}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="53">
   <si>
     <t>Customer</t>
   </si>
@@ -167,9 +167,6 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>Surface Finish</t>
-  </si>
-  <si>
     <t>Note</t>
   </si>
   <si>
@@ -202,6 +199,15 @@
   <si>
     <t>Cannot be measured reliably</t>
   </si>
+  <si>
+    <t xml:space="preserve">  </t>
+  </si>
+  <si>
+    <t>Unfnished welding</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
 </sst>
 </file>
 
@@ -211,7 +217,7 @@
     <numFmt numFmtId="164" formatCode="0.00000"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
-    <numFmt numFmtId="168" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
@@ -552,7 +558,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -563,9 +569,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -639,6 +642,18 @@
     <xf numFmtId="1" fontId="4" fillId="3" borderId="13" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="7" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -651,27 +666,6 @@
     <xf numFmtId="166" fontId="7" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -679,6 +673,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4248,7 +4257,7 @@
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="26.140625" style="6" customWidth="1"/>
+    <col min="2" max="2" width="26.140625" style="5" customWidth="1"/>
     <col min="3" max="3" width="9.5703125" style="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="1" customWidth="1"/>
     <col min="5" max="5" width="13.140625" style="1" customWidth="1"/>
@@ -4260,122 +4269,122 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="8" t="s">
+      <c r="B1" s="6"/>
+      <c r="C1" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="21"/>
-      <c r="E1" s="22" t="s">
+      <c r="D1" s="20"/>
+      <c r="E1" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="23" t="s">
+      <c r="F1" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="G1" s="30" t="s">
+      <c r="G1" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="31"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="14"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="13"/>
     </row>
     <row r="2" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="12">
+      <c r="D2" s="11">
         <v>5</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="E2" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="32"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="18"/>
-      <c r="M2" s="14"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="13"/>
     </row>
     <row r="3" spans="1:13" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="11">
+      <c r="F3" s="10">
         <v>6</v>
       </c>
-      <c r="G3" s="32"/>
-      <c r="H3" s="33"/>
-      <c r="I3" s="15"/>
-      <c r="J3" s="15"/>
-      <c r="K3" s="15"/>
-      <c r="L3" s="19"/>
-      <c r="M3" s="15"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="36"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="18"/>
+      <c r="M3" s="14"/>
     </row>
     <row r="4" spans="1:13" ht="60" x14ac:dyDescent="0.25">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="25" t="s">
+      <c r="C4" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="27" t="s">
+      <c r="D4" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="27" t="s">
+      <c r="E4" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="25" t="s">
+      <c r="F4" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="28" t="s">
+      <c r="G4" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="28" t="s">
+      <c r="H4" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="I4" s="29" t="s">
+      <c r="I4" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="J4" s="29" t="s">
+      <c r="J4" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="K4" s="29" t="s">
+      <c r="K4" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="L4" s="29" t="s">
+      <c r="L4" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="M4" s="29" t="s">
+      <c r="M4" s="28" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4386,39 +4395,39 @@
       <c r="B5" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="39">
+      <c r="C5" s="31">
         <v>32</v>
       </c>
-      <c r="D5" s="40">
+      <c r="D5" s="32">
         <v>0.4</v>
       </c>
-      <c r="E5" s="40">
+      <c r="E5" s="32">
         <v>0.4</v>
       </c>
-      <c r="F5" s="40">
+      <c r="F5" s="32">
         <f>C5+D5</f>
         <v>32.4</v>
       </c>
-      <c r="G5" s="40">
+      <c r="G5" s="32">
         <f>C5-E5</f>
         <v>31.6</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I5" s="38">
+      <c r="I5" s="30">
         <v>31.73</v>
       </c>
-      <c r="J5" s="38">
+      <c r="J5" s="30">
         <v>32.1</v>
       </c>
-      <c r="K5" s="38">
+      <c r="K5" s="30">
         <v>31.89</v>
       </c>
-      <c r="L5" s="38">
+      <c r="L5" s="30">
         <v>31.9</v>
       </c>
-      <c r="M5" s="38">
+      <c r="M5" s="30">
         <v>31.89</v>
       </c>
     </row>
@@ -4429,39 +4438,39 @@
       <c r="B6" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="39">
+      <c r="C6" s="31">
         <v>5</v>
       </c>
-      <c r="D6" s="40">
+      <c r="D6" s="32">
         <v>0.4</v>
       </c>
-      <c r="E6" s="40">
+      <c r="E6" s="32">
         <v>0.4</v>
       </c>
-      <c r="F6" s="40">
+      <c r="F6" s="32">
         <f>C6+D6</f>
         <v>5.4</v>
       </c>
-      <c r="G6" s="40">
+      <c r="G6" s="32">
         <f>C6-E6</f>
         <v>4.5999999999999996</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I6" s="38">
+      <c r="I6" s="30">
         <v>5.01</v>
       </c>
-      <c r="J6" s="38">
+      <c r="J6" s="30">
         <v>5.04</v>
       </c>
-      <c r="K6" s="38">
+      <c r="K6" s="30">
         <v>5.0199999999999996</v>
       </c>
-      <c r="L6" s="38">
+      <c r="L6" s="30">
         <v>5.08</v>
       </c>
-      <c r="M6" s="38">
+      <c r="M6" s="30">
         <v>5.01</v>
       </c>
     </row>
@@ -4472,39 +4481,39 @@
       <c r="B7" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="39">
+      <c r="C7" s="31">
         <v>1.3</v>
       </c>
-      <c r="D7" s="40">
+      <c r="D7" s="32">
         <v>0</v>
       </c>
-      <c r="E7" s="40">
+      <c r="E7" s="32">
         <v>0.4</v>
       </c>
-      <c r="F7" s="40">
+      <c r="F7" s="32">
         <f t="shared" ref="F7:F11" si="0">C7+D7</f>
         <v>1.3</v>
       </c>
-      <c r="G7" s="40">
+      <c r="G7" s="32">
         <f t="shared" ref="G7:G11" si="1">C7-E7</f>
         <v>0.9</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I7" s="38">
+      <c r="I7" s="30">
         <v>1.85</v>
       </c>
-      <c r="J7" s="38">
+      <c r="J7" s="30">
         <v>0.93</v>
       </c>
-      <c r="K7" s="38">
+      <c r="K7" s="30">
         <v>1.57</v>
       </c>
-      <c r="L7" s="38">
+      <c r="L7" s="30">
         <v>1.23</v>
       </c>
-      <c r="M7" s="38">
+      <c r="M7" s="30">
         <v>1.2</v>
       </c>
     </row>
@@ -4515,39 +4524,39 @@
       <c r="B8" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="39">
+      <c r="C8" s="31">
         <v>5.8</v>
       </c>
-      <c r="D8" s="40">
+      <c r="D8" s="32">
         <v>0.8</v>
       </c>
-      <c r="E8" s="40">
+      <c r="E8" s="32">
         <v>0.8</v>
       </c>
-      <c r="F8" s="40">
+      <c r="F8" s="32">
         <f t="shared" si="0"/>
         <v>6.6</v>
       </c>
-      <c r="G8" s="40">
+      <c r="G8" s="32">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I8" s="38">
+      <c r="I8" s="30">
         <v>6.2</v>
       </c>
-      <c r="J8" s="38">
+      <c r="J8" s="30">
         <v>5.92</v>
       </c>
-      <c r="K8" s="38">
+      <c r="K8" s="30">
         <v>5.44</v>
       </c>
-      <c r="L8" s="38">
+      <c r="L8" s="30">
         <v>7.09</v>
       </c>
-      <c r="M8" s="38">
+      <c r="M8" s="30">
         <v>6.33</v>
       </c>
     </row>
@@ -4558,39 +4567,39 @@
       <c r="B9" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="39">
+      <c r="C9" s="31">
         <v>4</v>
       </c>
-      <c r="D9" s="40">
+      <c r="D9" s="32">
         <v>0.4</v>
       </c>
-      <c r="E9" s="40">
+      <c r="E9" s="32">
         <v>0.4</v>
       </c>
-      <c r="F9" s="40">
+      <c r="F9" s="32">
         <f t="shared" si="0"/>
         <v>4.4000000000000004</v>
       </c>
-      <c r="G9" s="40">
+      <c r="G9" s="32">
         <f t="shared" si="1"/>
         <v>3.6</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I9" s="38">
+      <c r="I9" s="30">
         <v>3.99</v>
       </c>
-      <c r="J9" s="38">
+      <c r="J9" s="30">
         <v>3.99</v>
       </c>
-      <c r="K9" s="38">
+      <c r="K9" s="30">
         <v>3.96</v>
       </c>
-      <c r="L9" s="38">
+      <c r="L9" s="30">
         <v>3.99</v>
       </c>
-      <c r="M9" s="38">
+      <c r="M9" s="30">
         <v>3.99</v>
       </c>
     </row>
@@ -4601,31 +4610,31 @@
       <c r="B10" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="39">
+      <c r="C10" s="31">
         <v>15</v>
       </c>
-      <c r="D10" s="40">
+      <c r="D10" s="32">
         <v>0.4</v>
       </c>
-      <c r="E10" s="40">
+      <c r="E10" s="32">
         <v>0.4</v>
       </c>
-      <c r="F10" s="40">
+      <c r="F10" s="32">
         <f t="shared" si="0"/>
         <v>15.4</v>
       </c>
-      <c r="G10" s="40">
+      <c r="G10" s="32">
         <f t="shared" si="1"/>
         <v>14.6</v>
       </c>
       <c r="H10" s="2"/>
-      <c r="I10" s="41" t="s">
-        <v>50</v>
-      </c>
-      <c r="J10" s="42"/>
-      <c r="K10" s="42"/>
-      <c r="L10" s="42"/>
-      <c r="M10" s="43"/>
+      <c r="I10" s="37" t="s">
+        <v>49</v>
+      </c>
+      <c r="J10" s="38"/>
+      <c r="K10" s="38"/>
+      <c r="L10" s="38"/>
+      <c r="M10" s="39"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
@@ -4634,31 +4643,41 @@
       <c r="B11" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="39">
+      <c r="C11" s="31">
         <v>4</v>
       </c>
-      <c r="D11" s="40">
+      <c r="D11" s="32">
         <v>0.4</v>
       </c>
-      <c r="E11" s="40">
+      <c r="E11" s="32">
         <v>0.4</v>
       </c>
-      <c r="F11" s="40">
+      <c r="F11" s="32">
         <f t="shared" si="0"/>
         <v>4.4000000000000004</v>
       </c>
-      <c r="G11" s="40">
+      <c r="G11" s="32">
         <f t="shared" si="1"/>
         <v>3.6</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="I11" s="38"/>
-      <c r="J11" s="38"/>
-      <c r="K11" s="38"/>
-      <c r="L11" s="38"/>
-      <c r="M11" s="38"/>
+      <c r="I11" s="30">
+        <v>5.2958999999999996</v>
+      </c>
+      <c r="J11" s="30">
+        <v>5.4066000000000001</v>
+      </c>
+      <c r="K11" s="30">
+        <v>5.1844999999999999</v>
+      </c>
+      <c r="L11" s="30">
+        <v>5.2827999999999999</v>
+      </c>
+      <c r="M11" s="30">
+        <v>5.5214999999999996</v>
+      </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
@@ -4667,39 +4686,39 @@
       <c r="B12" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C12" s="39">
+      <c r="C12" s="31">
         <v>20</v>
       </c>
-      <c r="D12" s="40">
+      <c r="D12" s="32">
         <v>0.4</v>
       </c>
-      <c r="E12" s="40">
+      <c r="E12" s="32">
         <v>0.4</v>
       </c>
-      <c r="F12" s="40">
+      <c r="F12" s="32">
         <f t="shared" ref="F12:F30" si="2">C12+D12</f>
         <v>20.399999999999999</v>
       </c>
-      <c r="G12" s="40">
+      <c r="G12" s="32">
         <f t="shared" ref="G12:G30" si="3">C12-E12</f>
         <v>19.600000000000001</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I12" s="38">
+      <c r="I12" s="30">
         <v>20.39</v>
       </c>
-      <c r="J12" s="38">
+      <c r="J12" s="30">
         <v>20.32</v>
       </c>
-      <c r="K12" s="38">
+      <c r="K12" s="30">
         <v>20.13</v>
       </c>
-      <c r="L12" s="38">
+      <c r="L12" s="30">
         <v>20.09</v>
       </c>
-      <c r="M12" s="38">
+      <c r="M12" s="30">
         <v>20.22</v>
       </c>
     </row>
@@ -4710,31 +4729,41 @@
       <c r="B13" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="39">
+      <c r="C13" s="31">
         <v>7.5</v>
       </c>
-      <c r="D13" s="40">
+      <c r="D13" s="32">
         <v>0.4</v>
       </c>
-      <c r="E13" s="40">
+      <c r="E13" s="32">
         <v>0.4</v>
       </c>
-      <c r="F13" s="40">
+      <c r="F13" s="32">
         <f t="shared" si="2"/>
         <v>7.9</v>
       </c>
-      <c r="G13" s="40">
+      <c r="G13" s="32">
         <f t="shared" si="3"/>
         <v>7.1</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="I13" s="38"/>
-      <c r="J13" s="38"/>
-      <c r="K13" s="38"/>
-      <c r="L13" s="38"/>
-      <c r="M13" s="38"/>
+      <c r="I13" s="30">
+        <v>7.5175999999999998</v>
+      </c>
+      <c r="J13" s="30">
+        <v>7.5317999999999996</v>
+      </c>
+      <c r="K13" s="30">
+        <v>7.4886999999999997</v>
+      </c>
+      <c r="L13" s="30">
+        <v>7.5125000000000002</v>
+      </c>
+      <c r="M13" s="30">
+        <v>7.4983000000000004</v>
+      </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
@@ -4743,39 +4772,39 @@
       <c r="B14" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="39">
+      <c r="C14" s="31">
         <v>15</v>
       </c>
-      <c r="D14" s="40">
+      <c r="D14" s="32">
         <v>0.4</v>
       </c>
-      <c r="E14" s="40">
+      <c r="E14" s="32">
         <v>0.4</v>
       </c>
-      <c r="F14" s="40">
+      <c r="F14" s="32">
         <f t="shared" si="2"/>
         <v>15.4</v>
       </c>
-      <c r="G14" s="40">
+      <c r="G14" s="32">
         <f t="shared" si="3"/>
         <v>14.6</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I14" s="38">
+      <c r="I14" s="30">
         <v>15.06</v>
       </c>
-      <c r="J14" s="38">
+      <c r="J14" s="30">
         <v>15.08</v>
       </c>
-      <c r="K14" s="38">
+      <c r="K14" s="30">
         <v>15.06</v>
       </c>
-      <c r="L14" s="38">
+      <c r="L14" s="30">
         <v>14.99</v>
       </c>
-      <c r="M14" s="38">
+      <c r="M14" s="30">
         <v>15.05</v>
       </c>
     </row>
@@ -4786,31 +4815,41 @@
       <c r="B15" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="39">
+      <c r="C15" s="31">
         <v>5</v>
       </c>
-      <c r="D15" s="40">
+      <c r="D15" s="32">
         <v>0.4</v>
       </c>
-      <c r="E15" s="40">
+      <c r="E15" s="32">
         <v>0.4</v>
       </c>
-      <c r="F15" s="40">
+      <c r="F15" s="32">
         <f t="shared" si="2"/>
         <v>5.4</v>
       </c>
-      <c r="G15" s="40">
+      <c r="G15" s="32">
         <f t="shared" si="3"/>
         <v>4.5999999999999996</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="I15" s="38"/>
-      <c r="J15" s="38"/>
-      <c r="K15" s="38"/>
-      <c r="L15" s="38"/>
-      <c r="M15" s="38"/>
+      <c r="I15" s="30">
+        <v>4.8517999999999999</v>
+      </c>
+      <c r="J15" s="30">
+        <v>4.6929999999999996</v>
+      </c>
+      <c r="K15" s="30">
+        <v>4.6965000000000003</v>
+      </c>
+      <c r="L15" s="30">
+        <v>4.9325999999999999</v>
+      </c>
+      <c r="M15" s="30">
+        <v>4.9139999999999997</v>
+      </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
@@ -4819,39 +4858,39 @@
       <c r="B16" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="39">
+      <c r="C16" s="31">
         <v>5</v>
       </c>
-      <c r="D16" s="40">
+      <c r="D16" s="32">
         <v>0.4</v>
       </c>
-      <c r="E16" s="40">
+      <c r="E16" s="32">
         <v>0.4</v>
       </c>
-      <c r="F16" s="40">
+      <c r="F16" s="32">
         <f t="shared" si="2"/>
         <v>5.4</v>
       </c>
-      <c r="G16" s="40">
+      <c r="G16" s="32">
         <f t="shared" si="3"/>
         <v>4.5999999999999996</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I16" s="38">
+      <c r="I16" s="30">
         <v>4.99</v>
       </c>
-      <c r="J16" s="38">
+      <c r="J16" s="30">
         <v>5.0199999999999996</v>
       </c>
-      <c r="K16" s="38">
+      <c r="K16" s="30">
         <v>4.9800000000000004</v>
       </c>
-      <c r="L16" s="38">
+      <c r="L16" s="30">
         <v>4.9800000000000004</v>
       </c>
-      <c r="M16" s="38">
+      <c r="M16" s="30">
         <v>4.99</v>
       </c>
     </row>
@@ -4862,39 +4901,39 @@
       <c r="B17" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="39">
+      <c r="C17" s="31">
         <v>25</v>
       </c>
-      <c r="D17" s="40">
+      <c r="D17" s="32">
         <v>0.4</v>
       </c>
-      <c r="E17" s="40">
+      <c r="E17" s="32">
         <v>0.4</v>
       </c>
-      <c r="F17" s="40">
+      <c r="F17" s="32">
         <f t="shared" si="2"/>
         <v>25.4</v>
       </c>
-      <c r="G17" s="40">
+      <c r="G17" s="32">
         <f t="shared" si="3"/>
         <v>24.6</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I17" s="38">
+      <c r="I17" s="30">
         <v>24.69</v>
       </c>
-      <c r="J17" s="38">
+      <c r="J17" s="30">
         <v>24.89</v>
       </c>
-      <c r="K17" s="38">
+      <c r="K17" s="30">
         <v>24.8</v>
       </c>
-      <c r="L17" s="38">
+      <c r="L17" s="30">
         <v>24.88</v>
       </c>
-      <c r="M17" s="38">
+      <c r="M17" s="30">
         <v>24.92</v>
       </c>
     </row>
@@ -4905,31 +4944,41 @@
       <c r="B18" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="39">
+      <c r="C18" s="31">
         <v>2.5</v>
       </c>
-      <c r="D18" s="40">
+      <c r="D18" s="32">
         <v>0.4</v>
       </c>
-      <c r="E18" s="40">
+      <c r="E18" s="32">
         <v>0.4</v>
       </c>
-      <c r="F18" s="40">
+      <c r="F18" s="32">
         <f t="shared" si="2"/>
         <v>2.9</v>
       </c>
-      <c r="G18" s="40">
+      <c r="G18" s="32">
         <f t="shared" si="3"/>
         <v>2.1</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="I18" s="38"/>
-      <c r="J18" s="38"/>
-      <c r="K18" s="38"/>
-      <c r="L18" s="38"/>
-      <c r="M18" s="38"/>
+      <c r="I18" s="30">
+        <v>2.3121</v>
+      </c>
+      <c r="J18" s="30">
+        <v>2.7088999999999999</v>
+      </c>
+      <c r="K18" s="30">
+        <v>2.4300000000000002</v>
+      </c>
+      <c r="L18" s="30">
+        <v>2.4119000000000002</v>
+      </c>
+      <c r="M18" s="30">
+        <v>2.2446000000000002</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
@@ -4938,31 +4987,41 @@
       <c r="B19" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C19" s="39">
+      <c r="C19" s="31">
         <v>1</v>
       </c>
-      <c r="D19" s="40">
+      <c r="D19" s="32">
         <v>0.4</v>
       </c>
-      <c r="E19" s="40">
+      <c r="E19" s="32">
         <v>0.4</v>
       </c>
-      <c r="F19" s="40">
+      <c r="F19" s="32">
         <f t="shared" si="2"/>
         <v>1.4</v>
       </c>
-      <c r="G19" s="40">
+      <c r="G19" s="32">
         <f t="shared" si="3"/>
         <v>0.6</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="I19" s="38"/>
-      <c r="J19" s="38"/>
-      <c r="K19" s="38"/>
-      <c r="L19" s="38"/>
-      <c r="M19" s="38"/>
+      <c r="I19" s="30">
+        <v>1.3513999999999999</v>
+      </c>
+      <c r="J19" s="30">
+        <v>1.3225</v>
+      </c>
+      <c r="K19" s="30">
+        <v>1.3911</v>
+      </c>
+      <c r="L19" s="30">
+        <v>1.3142</v>
+      </c>
+      <c r="M19" s="30">
+        <v>1.2149000000000001</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
@@ -4971,39 +5030,39 @@
       <c r="B20" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C20" s="39">
+      <c r="C20" s="31">
         <v>0.5</v>
       </c>
-      <c r="D20" s="40">
+      <c r="D20" s="32">
         <v>0.4</v>
       </c>
-      <c r="E20" s="40">
+      <c r="E20" s="32">
         <v>0.4</v>
       </c>
-      <c r="F20" s="40">
+      <c r="F20" s="32">
         <f t="shared" si="2"/>
         <v>0.9</v>
       </c>
-      <c r="G20" s="40">
+      <c r="G20" s="32">
         <f t="shared" si="3"/>
         <v>9.9999999999999978E-2</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I20" s="38">
+      <c r="I20" s="30">
         <v>0.5</v>
       </c>
-      <c r="J20" s="38">
+      <c r="J20" s="30">
         <v>0.49</v>
       </c>
-      <c r="K20" s="38">
+      <c r="K20" s="30">
         <v>0.49</v>
       </c>
-      <c r="L20" s="38">
+      <c r="L20" s="30">
         <v>0.48</v>
       </c>
-      <c r="M20" s="38">
+      <c r="M20" s="30">
         <v>0.49</v>
       </c>
     </row>
@@ -5014,31 +5073,31 @@
       <c r="B21" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="39">
+      <c r="C21" s="31">
         <v>15.5</v>
       </c>
-      <c r="D21" s="40">
+      <c r="D21" s="32">
         <v>0.4</v>
       </c>
-      <c r="E21" s="40">
+      <c r="E21" s="32">
         <v>0.4</v>
       </c>
-      <c r="F21" s="40">
+      <c r="F21" s="32">
         <f t="shared" si="2"/>
         <v>15.9</v>
       </c>
-      <c r="G21" s="40">
+      <c r="G21" s="32">
         <f t="shared" si="3"/>
         <v>15.1</v>
       </c>
-      <c r="H21" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="I21" s="38"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="37" t="s">
+        <v>49</v>
+      </c>
       <c r="J21" s="38"/>
       <c r="K21" s="38"/>
       <c r="L21" s="38"/>
-      <c r="M21" s="38"/>
+      <c r="M21" s="39"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
@@ -5047,31 +5106,31 @@
       <c r="B22" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C22" s="39">
+      <c r="C22" s="31">
         <v>21</v>
       </c>
-      <c r="D22" s="40">
+      <c r="D22" s="32">
         <v>0.4</v>
       </c>
-      <c r="E22" s="40">
+      <c r="E22" s="32">
         <v>0.4</v>
       </c>
-      <c r="F22" s="40">
+      <c r="F22" s="32">
         <f t="shared" si="2"/>
         <v>21.4</v>
       </c>
-      <c r="G22" s="40">
+      <c r="G22" s="32">
         <f t="shared" si="3"/>
         <v>20.6</v>
       </c>
-      <c r="H22" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="I22" s="38"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="37" t="s">
+        <v>49</v>
+      </c>
       <c r="J22" s="38"/>
       <c r="K22" s="38"/>
       <c r="L22" s="38"/>
-      <c r="M22" s="38"/>
+      <c r="M22" s="39"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
@@ -5080,31 +5139,31 @@
       <c r="B23" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C23" s="39">
+      <c r="C23" s="31">
         <v>25.5</v>
       </c>
-      <c r="D23" s="40">
+      <c r="D23" s="32">
         <v>0.4</v>
       </c>
-      <c r="E23" s="40">
+      <c r="E23" s="32">
         <v>0.4</v>
       </c>
-      <c r="F23" s="40">
+      <c r="F23" s="32">
         <f t="shared" si="2"/>
         <v>25.9</v>
       </c>
-      <c r="G23" s="40">
+      <c r="G23" s="32">
         <f t="shared" si="3"/>
         <v>25.1</v>
       </c>
       <c r="H23" s="2"/>
-      <c r="I23" s="41" t="s">
-        <v>50</v>
-      </c>
-      <c r="J23" s="42"/>
-      <c r="K23" s="42"/>
-      <c r="L23" s="42"/>
-      <c r="M23" s="43"/>
+      <c r="I23" s="37" t="s">
+        <v>49</v>
+      </c>
+      <c r="J23" s="38"/>
+      <c r="K23" s="38"/>
+      <c r="L23" s="38"/>
+      <c r="M23" s="39"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
@@ -5113,31 +5172,41 @@
       <c r="B24" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C24" s="39">
+      <c r="C24" s="31">
         <v>1</v>
       </c>
-      <c r="D24" s="40">
+      <c r="D24" s="32">
         <v>0.4</v>
       </c>
-      <c r="E24" s="40">
+      <c r="E24" s="32">
         <v>0.4</v>
       </c>
-      <c r="F24" s="40">
+      <c r="F24" s="32">
         <f t="shared" si="2"/>
         <v>1.4</v>
       </c>
-      <c r="G24" s="40">
+      <c r="G24" s="32">
         <f t="shared" si="3"/>
         <v>0.6</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="I24" s="38"/>
-      <c r="J24" s="38"/>
-      <c r="K24" s="38"/>
-      <c r="L24" s="38"/>
-      <c r="M24" s="38"/>
+      <c r="I24" s="30">
+        <v>1.0857000000000001</v>
+      </c>
+      <c r="J24" s="30">
+        <v>1.1261000000000001</v>
+      </c>
+      <c r="K24" s="30">
+        <v>1.1600999999999999</v>
+      </c>
+      <c r="L24" s="30">
+        <v>1.1285000000000001</v>
+      </c>
+      <c r="M24" s="30">
+        <v>1.2565</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
@@ -5146,39 +5215,39 @@
       <c r="B25" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C25" s="39">
+      <c r="C25" s="31">
         <v>1.6</v>
       </c>
-      <c r="D25" s="40">
+      <c r="D25" s="32">
         <v>0.4</v>
       </c>
-      <c r="E25" s="40">
+      <c r="E25" s="32">
         <v>0.4</v>
       </c>
-      <c r="F25" s="40">
+      <c r="F25" s="32">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="G25" s="40">
+      <c r="G25" s="32">
         <f t="shared" si="3"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I25" s="38">
+      <c r="I25" s="30">
         <v>1.66</v>
       </c>
-      <c r="J25" s="38">
+      <c r="J25" s="30">
         <v>1.54</v>
       </c>
-      <c r="K25" s="38">
+      <c r="K25" s="30">
         <v>1.57</v>
       </c>
-      <c r="L25" s="38">
+      <c r="L25" s="30">
         <v>1.56</v>
       </c>
-      <c r="M25" s="38">
+      <c r="M25" s="30">
         <v>1.55</v>
       </c>
     </row>
@@ -5189,39 +5258,39 @@
       <c r="B26" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="39">
+      <c r="C26" s="31">
         <v>15</v>
       </c>
-      <c r="D26" s="40">
+      <c r="D26" s="32">
         <v>0</v>
       </c>
-      <c r="E26" s="40">
+      <c r="E26" s="32">
         <v>0.5</v>
       </c>
-      <c r="F26" s="40">
+      <c r="F26" s="32">
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-      <c r="G26" s="40">
+      <c r="G26" s="32">
         <f t="shared" si="3"/>
         <v>14.5</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I26" s="38">
+      <c r="I26" s="30">
         <v>14.97</v>
       </c>
-      <c r="J26" s="38">
+      <c r="J26" s="30">
         <v>14.98</v>
       </c>
-      <c r="K26" s="38">
+      <c r="K26" s="30">
         <v>15</v>
       </c>
-      <c r="L26" s="38">
+      <c r="L26" s="30">
         <v>14.97</v>
       </c>
-      <c r="M26" s="38">
+      <c r="M26" s="30">
         <v>14.97</v>
       </c>
     </row>
@@ -5232,39 +5301,39 @@
       <c r="B27" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C27" s="39">
+      <c r="C27" s="31">
         <v>6.5</v>
       </c>
-      <c r="D27" s="40">
+      <c r="D27" s="32">
         <v>0.4</v>
       </c>
-      <c r="E27" s="40">
+      <c r="E27" s="32">
         <v>0.4</v>
       </c>
-      <c r="F27" s="40">
+      <c r="F27" s="32">
         <f t="shared" si="2"/>
         <v>6.9</v>
       </c>
-      <c r="G27" s="40">
+      <c r="G27" s="32">
         <f t="shared" si="3"/>
         <v>6.1</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I27" s="38">
+      <c r="I27" s="30">
         <v>6.46</v>
       </c>
-      <c r="J27" s="38">
+      <c r="J27" s="30">
         <v>6.47</v>
       </c>
-      <c r="K27" s="38">
+      <c r="K27" s="30">
         <v>6.42</v>
       </c>
-      <c r="L27" s="38">
+      <c r="L27" s="30">
         <v>6.4</v>
       </c>
-      <c r="M27" s="38">
+      <c r="M27" s="30">
         <v>6.45</v>
       </c>
     </row>
@@ -5275,39 +5344,39 @@
       <c r="B28" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C28" s="39">
+      <c r="C28" s="31">
         <v>6</v>
       </c>
-      <c r="D28" s="40">
+      <c r="D28" s="32">
         <v>0.1</v>
       </c>
-      <c r="E28" s="40">
+      <c r="E28" s="32">
         <v>0.1</v>
       </c>
-      <c r="F28" s="40">
+      <c r="F28" s="32">
         <f t="shared" si="2"/>
         <v>6.1</v>
       </c>
-      <c r="G28" s="40">
+      <c r="G28" s="32">
         <f t="shared" si="3"/>
         <v>5.9</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I28" s="38">
+      <c r="I28" s="30">
         <v>6.07</v>
       </c>
-      <c r="J28" s="38">
+      <c r="J28" s="30">
         <v>5.93</v>
       </c>
-      <c r="K28" s="38">
+      <c r="K28" s="30">
         <v>5.98</v>
       </c>
-      <c r="L28" s="38">
+      <c r="L28" s="30">
         <v>5.96</v>
       </c>
-      <c r="M28" s="38">
+      <c r="M28" s="30">
         <v>6.01</v>
       </c>
     </row>
@@ -5318,39 +5387,39 @@
       <c r="B29" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C29" s="39">
+      <c r="C29" s="31">
         <v>3</v>
       </c>
-      <c r="D29" s="40">
+      <c r="D29" s="32">
         <v>0.4</v>
       </c>
-      <c r="E29" s="40">
+      <c r="E29" s="32">
         <v>0.4</v>
       </c>
-      <c r="F29" s="40">
+      <c r="F29" s="32">
         <f t="shared" si="2"/>
         <v>3.4</v>
       </c>
-      <c r="G29" s="40">
+      <c r="G29" s="32">
         <f t="shared" si="3"/>
         <v>2.6</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I29" s="38">
+      <c r="I29" s="30">
         <v>2.94</v>
       </c>
-      <c r="J29" s="38">
+      <c r="J29" s="30">
         <v>2.96</v>
       </c>
-      <c r="K29" s="38">
+      <c r="K29" s="30">
         <v>2.99</v>
       </c>
-      <c r="L29" s="38">
+      <c r="L29" s="30">
         <v>2.97</v>
       </c>
-      <c r="M29" s="38">
+      <c r="M29" s="30">
         <v>2.95</v>
       </c>
     </row>
@@ -5361,39 +5430,39 @@
       <c r="B30" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C30" s="39">
+      <c r="C30" s="31">
         <v>5</v>
       </c>
-      <c r="D30" s="40">
+      <c r="D30" s="32">
         <v>0.4</v>
       </c>
-      <c r="E30" s="40">
+      <c r="E30" s="32">
         <v>0.4</v>
       </c>
-      <c r="F30" s="40">
+      <c r="F30" s="32">
         <f t="shared" si="2"/>
         <v>5.4</v>
       </c>
-      <c r="G30" s="40">
+      <c r="G30" s="32">
         <f t="shared" si="3"/>
         <v>4.5999999999999996</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I30" s="38">
+      <c r="I30" s="30">
         <v>4.8600000000000003</v>
       </c>
-      <c r="J30" s="38">
+      <c r="J30" s="30">
         <v>4.99</v>
       </c>
-      <c r="K30" s="38">
+      <c r="K30" s="30">
         <v>4.8899999999999997</v>
       </c>
-      <c r="L30" s="38">
+      <c r="L30" s="30">
         <v>4.92</v>
       </c>
-      <c r="M30" s="38">
+      <c r="M30" s="30">
         <v>4.99</v>
       </c>
       <c r="N30" s="1" t="s">
@@ -5401,13 +5470,15 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="5">
     <mergeCell ref="G1:H3"/>
     <mergeCell ref="I10:M10"/>
     <mergeCell ref="I23:M23"/>
+    <mergeCell ref="I21:M21"/>
+    <mergeCell ref="I22:M22"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
-  <conditionalFormatting sqref="I5:M9 I11:M22 I24:M30">
+  <conditionalFormatting sqref="I5:M9 I11:M20 I24:M30">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="notBetween">
       <formula>$G5</formula>
       <formula>$F5</formula>
@@ -5428,7 +5499,7 @@
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="26.140625" style="6" customWidth="1"/>
+    <col min="2" max="2" width="26.140625" style="5" customWidth="1"/>
     <col min="3" max="3" width="9.5703125" style="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="1" customWidth="1"/>
     <col min="5" max="5" width="13.140625" style="1" customWidth="1"/>
@@ -5438,88 +5509,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="8" t="s">
+      <c r="B1" s="6"/>
+      <c r="C1" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="21"/>
-      <c r="E1" s="22" t="s">
+      <c r="D1" s="20"/>
+      <c r="E1" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="37">
+      <c r="F1" s="29">
         <f ca="1">TODAY()</f>
-        <v>46129</v>
-      </c>
-      <c r="G1" s="36" t="s">
-        <v>47</v>
+        <v>46132</v>
+      </c>
+      <c r="G1" s="40" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="12">
+      <c r="D2" s="11">
         <v>75</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="E2" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="35"/>
+      <c r="G2" s="41"/>
     </row>
     <row r="3" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="11">
+      <c r="F3" s="10">
         <v>6</v>
       </c>
-      <c r="G3" s="34"/>
+      <c r="G3" s="42"/>
     </row>
     <row r="4" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="25" t="s">
+      <c r="A4" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="25" t="s">
+      <c r="B4" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="D4" s="27" t="s">
+      <c r="C4" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="E4" s="27" t="s">
+      <c r="D4" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="F4" s="25" t="s">
+      <c r="E4" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="G4" s="28" t="s">
+      <c r="F4" s="24" t="s">
         <v>40</v>
+      </c>
+      <c r="G4" s="27" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -5527,14 +5598,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C5" s="5">
+        <v>48</v>
+      </c>
+      <c r="C5" s="43">
         <f>$D$2</f>
         <v>75</v>
       </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2">
+      <c r="D5" s="44">
+        <v>0</v>
+      </c>
+      <c r="E5" s="44">
         <f>C5-D5</f>
         <v>75</v>
       </c>
@@ -5549,20 +5622,21 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C6" s="5">
+        <v>51</v>
+      </c>
+      <c r="C6" s="43">
         <f>$D$2</f>
         <v>75</v>
       </c>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2">
+      <c r="D6" s="44">
+        <v>1</v>
+      </c>
+      <c r="E6" s="44">
         <f>C6-D6</f>
-        <v>75</v>
-      </c>
-      <c r="F6" s="2" t="str">
-        <f>IF(D6=0, "PASS", "FAIL")</f>
-        <v>PASS</v>
+        <v>74</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>52</v>
       </c>
       <c r="G6" s="2"/>
     </row>
@@ -5571,14 +5645,16 @@
         <v>3</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C7" s="5">
+        <v>47</v>
+      </c>
+      <c r="C7" s="43">
         <f>$D$2</f>
         <v>75</v>
       </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2">
+      <c r="D7" s="44">
+        <v>0</v>
+      </c>
+      <c r="E7" s="44">
         <f>C7-D7</f>
         <v>75</v>
       </c>
@@ -5599,9 +5675,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9490EC76-6455-44B4-AA60-563ACC8D591D}">
-  <dimension ref="A1"/>
+  <dimension ref="S21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetData>
+    <row r="21" spans="19:19" x14ac:dyDescent="0.25">
+      <c r="S21" t="s">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
